--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0019.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0019.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Khi Resonance Liberation được kích hoạt, cộng thêm {0} tầng Giáp Sắt. Mỗi tầng tăng Tấn Công và Phòng Ngự thêm {1}, tối đa {2} tầng. Khi Resonator nhận sát thương, số tầng sẽ giảm đi {3}.</t>
+          <t>Khi Resonance Liberation được kích hoạt, cộng thêm {0} tầng Giáp Sắt. Mỗi tầng tăng ATK và Phòng Ngự thêm {1}, tối đa {2} tầng. Khi Resonator nhận sát thương, số tầng sẽ giảm đi {3}.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt Concerto Effect, Sát Thương Resonance Liberation tăng {0}% trong 10 giây. Có thể chồng chất tối đa 2 lần.</t>
+          <t>Sau khi kích hoạt Hiệu Ứng Concerto, Sát Thương Resonance Liberation tăng {0}% trong 10 giây. Có thể chồng chất tối đa 2 lần.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Khi gây Sát Thương Basic Attack, tăng thêm {1} Sát Thương Basic Attack, có thể chồng chất lên đến {2} lần. Hiệu ứng này kéo dài trong {3} giây và có thể kích hoạt {5} lần mỗi {4} giây.</t>
+          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Khi gây Sát Thương Đòn Basic Attack, tăng thêm {1} Sát Thương Đòn Basic Attack, có thể chồng chất lên đến {2} lần. Hiệu ứng này kéo dài trong {3} giây và có thể kích hoạt {5} lần mỗi {4} giây.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Thuộc Tính. Khi gây Sát Thương Resonance Skill, tăng Tấn Công thêm {1}, có thể tích lũy tối đa {2} lần. Hiệu ứng kéo dài trong {3} giây. Khi người sử dụng không ở trên chiến trường, Tấn Công của họ sẽ được tăng thêm {4}.</t>
+          <t>Tăng {0} Sát Thương Thuộc Tính. Khi gây Sát Thương Resonance Skill, tăng ATK thêm {1}, có thể tích lũy tối đa {2} lần. Hiệu ứng kéo dài trong {3} giây. Khi người sử dụng không ở trên chiến trường, ATK của họ sẽ được tăng thêm {4}.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Khi sử dụng Resonance Skill, nếu HP của Resonator dưới {0}, sẽ hồi {1} HP tối đa. Hiệu ứng này có thể kích hoạt {3} lần mỗi {2} giây. Nếu HP của Resonator trên {4}, Tấn Công sẽ tăng {5}, kéo dài trong {6} giây.</t>
+          <t>Khi sử dụng Resonance Skill, nếu HP của Resonator dưới {0}, sẽ hồi {1} HP tối đa. Hiệu ứng này có thể kích hoạt {3} lần mỗi {2} giây. Nếu HP của Resonator trên {4}, ATK sẽ tăng {5}, kéo dài trong {6} giây.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Increase HP thêm {0}. Hồi {1} Concerto Energy khi sử dụng Resonance Liberation. Hiệu ứng này có thể kích hoạt {3} lần mỗi {2} giây. Khi sử dụng Resonance Skill có khả năng hồi máu, tăng Tấn Công cho các Resonator đồng đội gần đó thêm {4} trong {5} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Tăng HP thêm {0}. Hồi {1} Concerto Energy khi sử dụng Resonance Liberation. Hiệu ứng này có thể kích hoạt {3} lần mỗi {2} giây. Khi sử dụng Resonance Skill có khả năng hồi máu, tăng ATK cho các Cộng Hưởng Giả đồng đội gần đó thêm {4} trong {5} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ tăng Tấn Công của người sử dụng thêm {0} và HP thêm {1}, hiệu ứng kéo dài {2} giây.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ tăng ATK của người sử dụng thêm {0} và HP thêm {1}, hiệu ứng kéo dài {2} giây.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tăng Hiệu Ứng Sát Thương Basic Attack và Heavy Attack lên {0}.</t>
+          <t>Tăng Hiệu Ứng Sát Thương Đòn Basic Attack và Đòn Heavy Attack lên {0}.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Khi kích hoạt Concerto Effect, Sát Thương Resonance Liberation tăng {0}% trong 10 giây, có thể chồng chất lên đến 2 lần.</t>
+          <t>Khi kích hoạt Hiệu Ứng Concerto, Sát Thương Resonance Liberation tăng {0}% trong 10 giây, có thể chồng chất lên đến 2 lần.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Khi gây sát thương bằng Basic Attack hoặc Heavy Attack, tăng Hiệu Quả Chữa Trị lên {0}, có thể tích lũy tối đa {2} lần. Hiệu ứng này kéo dài {1} giây và có thể kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>Khi gây DMG bằng Đòn Basic Attack hoặc Đòn Heavy Attack, tăng Hiệu Quả Chữa Trị lên {0}, có thể tích lũy tối đa {2} lần. Hiệu ứng này kéo dài {1} giây và có thể kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tấn Công của người sử dụng lên {0}, kéo dài trong {1} giây.</t>
+          <t>Kích hoạt Resonance Liberation tăng ATK của người sử dụng lên {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng Tấn Công lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
+          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng ATK lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Increases ATK by {0}. Sau khi người sử dụng gây Fusion Burst hoặc Tune Strain - Shifting lên mục tiêu, Sát Thương Kỹ Năng Resonance Liberation của họ sẽ tăng thêm {1} trong {2} giây. Trong thời gian hiệu ứng này còn tác dụng, sau khi Resonators trong đội gây Fusion Burst hoặc Tune Strain - Shifting, Tấn Công của họ sẽ tăng thêm {3} trong {4} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Tăng ATK {0}. Sau khi người sử dụng gây Fusion Burst hoặc Tune Strain - Shifting lên mục tiêu, Sát Thương Kỹ Năng Giải Cứu Cộng Hưởng của họ sẽ tăng thêm {1} trong {2} giây. Trong thời gian hiệu ứng này còn tác dụng, sau khi Resonator trong đội gây Fusion Burst hoặc Tune Strain - Shifting, ATK của họ sẽ tăng thêm {3} trong {4} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chu Thiên Chính: Nội Shield Cuối Cùng</t>
+          <t>Chu Thiên Chính: Nội Khiên Cuối Cùng</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Thiếu Tá Zhoutian: Shield Bảo Vệ Cuối Cùng Ngoại Vi</t>
+          <t>Thiếu Tá Zhoutian: Khiên Bảo Vệ Cuối Cùng Ngoại Vi</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hồi Phục Khiên</t>
+          <t>Khiên Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Thời Gian Shield</t>
+          <t>Thời Gian Khiên</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Giai Đoạn 4 Tấn Công Cơ Bản: Chi</t>
+          <t>Cú Đòn Cơ Bản Hạng 4: Khí</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Heavy Attack: Khí</t>
+          <t>Đòn Heavy Attack: Khí</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Tinh Hoa Đạo: Chi</t>
+          <t>Tinh Hoa Đạo: Khí</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Khí Trầm Tĩnh: Chi</t>
+          <t>Luồng Gió Bình Yên: Khí</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Phản Đòn Chi: Chi</t>
+          <t>Phản kích Khí: Chi</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Chặn Chi: Chi</t>
+          <t>Phản Kích Chi: Chi</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Concerto Regen Punch Đẩy</t>
+          <t>Hồi Phục Concerto Đấm Đẩy</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Tiểu Chu Thiên Concerto Regen</t>
+          <t>Hồi phục Minor Zhoutian Concerto</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đại Chu Thiên: Inner Concerto Regen</t>
+          <t>Chu Thiên Chính: Inner Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đại Chu Thiên: Outer Concerto Regen</t>
+          <t>Thiếu Tá Zhoutian: Outer Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Kéo Nhượng Bộ Concerto Regen</t>
+          <t>Hồi Phục Khúc Concerto Kéo Dồn</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Xoáy Khí Nguyên Sơ: Khi Thanh Forte đầy, giữ {0} để liên tục tiêu hao Forte và nhận Shield</t>
+          <t>Xoáy Khí Nguyên Sơ: Khi Thanh Forte đầy, giữ {0} để liên tục tiêu hao Forte và nhận Khiên</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Basic Attack: Stormy Kicks - Trong trạng thái Under Striding Lion, nhấn {0} khi tiêu hao không quá 10 Forte Gauge</t>
+          <t>Basic Attack: Đòn Cước Bão Tố - Trong trạng thái Under Striding Lion, nhấn {0} khi tiêu hao không quá 10 Forte Gauge</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Cơn Cuồng Cosmos: Hỗn Loạn</t>
+          <t>Cơn Cuồng Vũ Trụ: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Hồi Phục Bản Giao Hưởng Giải Phóng Feather</t>
+          <t>Hồi Phục Bản Giao Hưởng Giải Phóng Lông Vũ</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{0} per segment</t>
+          <t>Tăng {0} mỗi phân đoạn</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Lá Chắn Value Cố Định Stage 3 Phản Đòn Định Thời</t>
+          <t>Lá Chắn Giá Trị Cố Định Giai Đoạn 3 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Khiên Phản Đòn Hẹn Giờ Giai Đoạn 1</t>
+          <t>Lá Chắn Giai Đoạn 1 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Khiên Phản Đòn Hẹn Giờ Giai Đoạn 2</t>
+          <t>Lá Chắn Giai Đoạn 2 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Khiên Phản Đòn Hẹn Giờ Giai Đoạn 3</t>
+          <t>Lá Chắn Giai Đoạn 3 Phản Đòn Định Thời</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Thời Gian Shield</t>
+          <t>Thời Gian Khiên</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Kẻ Đoạt Mạng: Umbra</t>
+          <t>Lifetaker: Umbra</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Basic Attack Stage 3</t>
+          <t>Umbra: Sát Thương Basic Attack Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Basic Attack Stage 4</t>
+          <t>Umbra: Sát Thương Basic Attack Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Basic Attack Stage 5</t>
+          <t>Umbra: Sát Thương Basic Attack Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Heavy Attack</t>
+          <t>Umbra: Heavy Attack DMG</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Umbra: DMG Kiếm Chém</t>
+          <t>Umbra: Sát Thương Kiếm Thoảng</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Umbra: Sát Thương Đòn Lao Xuống</t>
+          <t>Umbra: Plunging Attack DMG</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Umbra: DMG Phản Đòn Né Tránh</t>
+          <t>Umbra: Dodge Counter DMG</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Umbra: Tiêu Hao Thể Lực Heavy Attack</t>
+          <t>Umbra: Heavy Attack STA Cost</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Umbra: Tiêu Hao STA Lao Xuống</t>
+          <t>Umbra: Plunging STA Cost</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Umbra: DMG Kẻ Đoạt Mạng</t>
+          <t>Umbra: Sát Thương Hút Mạng</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Umbra: Thời Gian Cooldown Hút Mạng</t>
+          <t>Umbra: Lifetaker Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Kẻ Đoạt Mạng Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Lifetaker</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Hồi Phục Umbra Khoảnh Khắc Hủy Diệt</t>
+          <t>Hồi Phục Umbra - Khoảnh Khắc Hủy Diệt</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Hồi Phục Umbra Kiếm Cánh</t>
+          <t>Lưỡi Kiếm Bay - Hồi Phục Bóng Tối</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>"Photosynthesis Energy" Concerto Hồi Phục</t>
+          <t>"Năng Lượng Quang Hợp" Concerto Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>"Khúc Concerto "Messenger Tử Thần" - Hồi Phục"</t>
+          <t>"Khúc Concerto "Sứ Giả Tử Thần" - Hồi Phục"</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Tia Lửa Gầm Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Tia Lửa Âm Thanh</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>“Tinh Thần Sư Tử” Concerto Regen</t>
+          <t>"Khúc Tái Sinh \"Tinh Thần Sư Tử\""</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Mid-air Attack: Starflower Nở Stage 1</t>
+          <t>Mid-air Attack: Hoa Sao Nở Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Mid-air Attack: Starflower Nở Stage 2</t>
+          <t>Mid-air Attack: Hoa Sao Nở Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Mid-air Attack: Starflower Nở Stage 3</t>
+          <t>Mid-air Attack: Hoa Sao Nở Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{0} per hit</t>
+          <t>Tăng {0} mỗi lần trúng đích</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Heavy Attack: Hồi Phục Năng Lượng Bản Giao Hưởng "Concentration"</t>
+          <t>Đòn Heavy Attack: Hồi Phục Năng Lượng Bản Giao Hưởng "Tập Trung"</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Resonance Skill với "Concentration" hồi phục Concerto Energy.</t>
+          <t>Kỹ năng Cộng Hưởng với "Tập Trung" hồi phục Năng Lượng Concerto.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Resonance Regen Tấn Công Nặng “Tập Trung”</t>
+          <t>Đòn Tấn Công Mạnh "Tập Trung" Hồi Phục Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Thời Gian Glacier</t>
+          <t>Thời Gian Băng Hà</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Thời Gian Tồn Tại Ice Prism</t>
+          <t>Thời Gian Tồn Tại Lăng Kính Băng</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Thời Gian Ice Thorn Tồn Tại</t>
+          <t>Thời Gian Gai Băng Tồn Tại</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Heavy Attack: Tàn Phá: Khi Thanh Forte đầy, giữ {0}</t>
+          <t>Đòn Heavy Attack: Tàn Phá: Khi Thanh Forte đầy, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Tấn công để hồi phục &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;.</t>
+          <t>Tấn công để hồi phục &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; đạt 50%, sau khi thi triển &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;, tiêu hao &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Enhanced Sync Attack&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; đạt 50%, sau khi thi triển &lt;color=Highlight&gt;Giai Đoạn 4 Đòn Basic Attack&lt;/color&gt;, tiêu hao &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Đòn Sync Tăng Cường&lt;/color&gt; và khôi phục &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; đầy, sử dụng &lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt; sẽ khôi phục &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;. Khi cả &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; đều đầy, &lt;color=Highlight&gt;Resonance Liberation Finisher&lt;/color&gt; sẽ sẵn sàng.</t>
+          <t>Khi &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; đầy, sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack Tăng Cường&lt;/color&gt; sẽ khôi phục &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt;. Khi cả &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; đều đầy, &lt;color=Highlight&gt;Đòn Kết Thúc Resonance Liberation&lt;/color&gt; sẽ sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -8636,9 +8636,9 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Hồi phục Dòng Ichor khi Normal Attack và Resonance Skill trúng mục tiêu hoặc khi kích hoạt Intro Skill.
+          <t>Hồi phục Dòng Ichor khi Đòn Normal Attack và Resonance Skill trúng mục tiêu hoặc khi kích hoạt Kỹ Năng Khởi Động.
 Khi Dòng Ichor đầy, bước vào trạng thái &lt;color=Highlight&gt;Aureate Judge&lt;/color&gt;.
-Trong trạng thái &lt;color=Highlight&gt;Aureate Judge&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt; tăng hệ số sát thương. Mỗi lần kích hoạt sẽ tiêu hao 100 điểm Dòng Ichor.</t>
+Trong trạng thái &lt;color=Highlight&gt;Aureate Judge&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt; tăng hệ số DMG. Mỗi lần kích hoạt sẽ tiêu hao 100 điểm Dòng Ichor.</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Aureate Judge&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt; được tăng hệ số sát thương. Mỗi lần sử dụng sẽ tiêu hao 100 điểm Flow Ichor.</t>
+          <t>Trong &lt;color=Highlight&gt;Thẩm Phán Hoàng Kim&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Vòng Hào Quang Xử Án&lt;/color&gt; được tăng hệ số DMG. Mỗi lần sử dụng sẽ tiêu hao 100 điểm Dòng Chảy Ichor.</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Nhận được &lt;color=Highlight&gt;Rune: Trust&lt;/color&gt; khi &lt;color=Highlight&gt;Basic Attack - Elucidated&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Decipher&lt;/color&gt; trực tiếp trúng mục tiêu trong thời gian thi triển. Hoặc nhận được &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt; khi &lt;color=Highlight&gt;Resonance Skill - BIG BOOMY BOOM!&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill - Soliskin to the Aid&lt;/color&gt; trực tiếp trúng mục tiêu trong thời gian thi triển.</t>
+          <t>Nhận được &lt;color=Highlight&gt;Rune: Niềm Tin&lt;/color&gt; khi &lt;color=Highlight&gt;Đòn Basic Attack - Giải Thích&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter Tránh - Giải Mã&lt;/color&gt; trực tiếp trúng mục tiêu trong thời gian thi triển. Hoặc nhận được &lt;color=Highlight&gt;Rune: Lời Đáp&lt;/color&gt; khi &lt;color=Highlight&gt;Resonance Skill - BIG BOOMY BOOM!&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill - Soliskin Đến Cứu Vớt&lt;/color&gt; trực tiếp trúng mục tiêu trong thời gian thi triển.</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Full Stop&lt;/color&gt;, hồi phục 50 điểm &lt;color=Highlight&gt;Heavy Attack - Schemata of Runes&lt;/color&gt;, tối đa 100 điểm. Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đạt 100 điểm, giữ Resonance Skill để tiêu hao 100 điểm &lt;color=Highlight&gt;Full Stop&lt;/color&gt; và kích hoạt &lt;color=Highlight&gt;Forte Circuit - Learn My True Name&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Sơ Đồ Rune&lt;/color&gt;, hồi phục 50 điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, tối đa 100 điểm. Khi &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt; đạt 100 điểm, giữ Resonance Skill để tiêu hao 100 điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt; và kích hoạt &lt;color=Highlight&gt;Forte Circuit - Học Tên Thật Của Ta&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Resonators gần đó trong đội sử dụng Kỹ Năng Echo, Sigrika nhận được 10 điểm &lt;color=Highlight&gt;Soliskin Vitality&lt;/color&gt;, tối đa 60 điểm. Nếu &lt;color=Highlight&gt;Soliskin Vitality&lt;/color&gt; đạt 30 điểm khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Schemata of Runes&lt;/color&gt;, tiêu hao 30 điểm &lt;color=Highlight&gt;Soliskin Vitality&lt;/color&gt; để tăng sát thương.</t>
+          <t>Khi bất kỳ Resonator gần đó trong đội sử dụng Kỹ Năng Echo, Sigrika nhận được 10 điểm &lt;color=Highlight&gt;Sinh Khí Soliskin&lt;/color&gt;, tối đa 60 điểm. Nếu &lt;color=Highlight&gt;Sinh Khí Soliskin&lt;/color&gt; đạt 30 điểm khi sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Sơ Đồ Rune&lt;/color&gt;, tiêu hao 30 điểm &lt;color=Highlight&gt;Sinh Khí Soliskin&lt;/color&gt; để tăng sát thương.</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Stagecraft Form&lt;/color&gt;, tấn công mục tiêu sẽ nhận được &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Hình Thức Diễn Xuất&lt;/color&gt;, tấn công mục tiêu sẽ nhận được &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt;, tiêu hao &lt;color=Highlight&gt;Void Particle&lt;/color&gt; và chuyển hóa thành &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; để nạp cho &lt;color=Highlight&gt;Final Act - Breakdown Form&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Hình Thái Phân Rã&lt;/color&gt;, tiêu hao &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt; và chuyển hóa thành &lt;color=Highlight&gt;Điện Tích Đồng Dạng&lt;/color&gt; để nạp cho &lt;color=Highlight&gt;Hồi Kết - Hình Thái Phân Rã&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Entropy Shift&lt;/color&gt;, nhận &lt;color=Highlight&gt;Dark Cores&lt;/color&gt; theo thời gian, mở khóa &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Dịch Chuyển Entropy&lt;/color&gt;, nhận &lt;color=Highlight&gt;Lõi Hắc Ám&lt;/color&gt; theo thời gian, mở khóa &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Present Self&lt;/color&gt;, thi triển &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; và &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ hồi phục &lt;color=Highlight&gt;Dedication&lt;/color&gt; cho Thanh Forte. Khi &lt;color=Highlight&gt;Dedication&lt;/color&gt; đạt tối đa, Heavy Attack Nâng Cao &lt;color=Highlight&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt; và Resonance Liberation &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt; sẽ khả dụng. Thi triển &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt; sẽ đưa Hiyuki vào trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Bản Ngã Hiện Tại&lt;/color&gt;, thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Giai Đoạn 3 Bản Ngã Hiện Tại&lt;/color&gt; và &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ hồi phục &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt; cho Thanh Forte. Khi &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt; đạt tối đa, Đòn Heavy Attack Nâng Cao &lt;color=Highlight&gt;Đòn Heavy Attack - Mảnh Băng Giá: Bản Ngã Hiện Tại&lt;/color&gt; và Resonance Liberation &lt;color=Highlight&gt;Tuyên Bố: Tầm Nhìn Nội Tâm&lt;/color&gt; sẽ khả dụng. Thi triển &lt;color=Highlight&gt;Tuyên Bố: Tầm Nhìn Nội Tâm&lt;/color&gt; sẽ đưa Hiyuki vào trạng thái &lt;color=Highlight&gt;Bản Ngã Đã Tuyên Bố&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, Hiyuki phục hồi Đồng Hồ Forte &lt;color=Highlight&gt;Frostheart&lt;/color&gt; khi &lt;color=Highlight&gt;Normal Attack - Foreclaimed Self&lt;/color&gt; trúng mục tiêu hoặc khi thi triển Resonance Skill. Khi &lt;color=Highlight&gt;Frostheart&lt;/color&gt; đủ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt; sau khi Hiyuki thực hiện một số đòn tấn công nhất định, trong đó có thể thi triển &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt; bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, Hiyuki phục hồi Đồng Hồ Forte &lt;color=Highlight&gt;Frostheart&lt;/color&gt; khi &lt;color=Highlight&gt;Đòn Normal Attack - Foreclaimed Self&lt;/color&gt; trúng mục tiêu hoặc khi thi triển Resonance Skill. Khi &lt;color=Highlight&gt;Frostheart&lt;/color&gt; đủ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né để vào &lt;color=Highlight&gt;Iai Stance&lt;/color&gt; sau khi Hiyuki thực hiện một số đòn tấn công nhất định, trong đó có thể thi triển &lt;color=Highlight&gt;Đòn Basic Attack - Iai&lt;/color&gt; bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9354,8 +9354,8 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation - Stagecraft Form&lt;/color&gt; sẽ ban cho Denia &lt;color=Highlight&gt;Entropy Shift: Breakdown Form&lt;/color&gt;, làm tăng Tấn Công của cô.
-Kích hoạt &lt;color=Highlight&gt;Resonance Liberation - Breakdown Form&lt;/color&gt; sẽ ban cho Denia &lt;color=Highlight&gt;Entropy Shift: Stagecraft Form&lt;/color&gt;, liên tục hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation - Dạng Sân Khấu&lt;/color&gt; sẽ ban cho Denia &lt;color=Highlight&gt;Dịch Chuyển Entropy: Dạng Phân Rã&lt;/color&gt;, làm tăng ATK của cô.
+Kích hoạt &lt;color=Highlight&gt;Resonance Liberation - Dạng Phân Rã&lt;/color&gt; sẽ ban cho Denia &lt;color=Highlight&gt;Dịch Chuyển Entropy: Dạng Sân Khấu&lt;/color&gt;, liên tục hồi phục &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Heavy Attack: Kiếm Đâm: Giữ {0} + Nhấn {0} khi ở trạng thái tăng cường</t>
+          <t>Đòn Heavy Attack: Kiếm Đâm: Giữ {0} + Nhấn {0} khi ở trạng thái tăng cường</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>“Lòng Thương Xót” Resonance Regen</t>
+          <t>"Lòng thương xót" Hồi Phục Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>"Resonance "Messenger Tử Thần" - Hồi Phục"</t>
+          <t>"Cộng Hưởng "Sứ Giả Tử Thần" - Hồi Phục"</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>DMG Ánh Sáng Tràn</t>
+          <t>Sát Thương Ánh Sáng Tràn</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Thời Gian Incarnation</t>
+          <t>Thời Gian Hóa Thân</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Cooldown Ánh Sáng Tràn</t>
+          <t>Hồi Chiêu Ánh Sáng Tràn</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ánh Sáng Tràn Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Ánh Sáng Tràn</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Thời Gian Ánh Sáng Phong Chức</t>
+          <t>Thời Gian Phát Sáng Phong Ấn</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Incarnation - Sát Thương Attack 1 Basic 1</t>
+          <t>Hóa Thân - Sát Thương Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Incarnation - Sát Thương Basic Attack 2</t>
+          <t>Hóa Thân - Sát Thương Basic Attack 2</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Incarnation - Sát Thương Basic Attack 3</t>
+          <t>Hóa Thân - Sát Thương Basic Attack 3</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Incarnation - Sát Thương Basic Attack 4</t>
+          <t>Hóa Thân - Sát Thương Basic Attack 4</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>DMG Thần Quyền Lưỡi Liềm</t>
+          <t>Sát Thương Thần Nguyệt Lưỡi Liềm</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Incarnation - Sát Thương Heavy Attack</t>
+          <t>Hóa Thân - Sát Thương Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Incarnation - Thể Lực Tiêu Hao Khi Heavy Attack</t>
+          <t>Hóa Thân - STA Tiêu Hao Khi Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Giác Ngộ Quang Minh: DMG Tai Lửa Mặt Trời</t>
+          <t>Khải Tường: Solar Flare DMG</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Thần Thánh Lưỡi Liềm</t>
+          <t>Thời gian hồi Chiêu Thần Thánh Lưỡi Liềm</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Cooldown chiêu kỹ năng của Jinhsi</t>
+          <t>Thời gian hồi chiêu kỹ năng của Jinhsi</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Thần Quyền Lưỡi Liềm Concerto Regen</t>
+          <t>Khúc Phục Hồi Thần Thánh Lưỡi Liềm</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Giác Ngộ Quang Minh Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Khải Tường</t>
         </is>
       </c>
     </row>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hệ Số Nhân Bổ Sung Mỗi Lần Nóng Sáng</t>
+          <t>Hệ số nhân cộng thêm cho mỗi Incandescence</t>
         </is>
       </c>
     </row>
@@ -14692,7 +14692,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Thời Gian Đồng Điệu</t>
+          <t>Thời Gian Đồng Nhất</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Incarnation - Sát Thương Dodge Counter</t>
+          <t>Hóa Thân - Sát Thương Dodge Counter Tránh</t>
         </is>
       </c>
     </row>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Incarnation - Thể Lực Tiêu Hao Khi Dodge</t>
+          <t>Hóa Thân - STA Tiêu Hao Khi Né Tránh</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Tiếng Gầm Từ Tính Concerto Regen</t>
+          <t>Hồi Phục Giao Hưởng Hống Magnet</t>
         </is>
       </c>
     </row>
@@ -16122,7 +16122,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hành Quyết Sét Concerto Regen</t>
+          <t>Hồi Phục Khúc Hành Quyết Sét</t>
         </is>
       </c>
     </row>
@@ -16187,7 +16187,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Vụ Nổ Điện Từ Concerto Regen</t>
+          <t>Hồi Phục Khúc Nổ Điện Từ</t>
         </is>
       </c>
     </row>
@@ -16385,9 +16385,9 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Biến thành Rocksteady Guardian và bước vào Trạng Thái Dodge Đòn. Khi bị tấn công, gây Spectro DMG bằng {0} HP Tối Đa của Resonator, và thực hiện đòn tấn công tiếp theo gây Spectro DMG bằng {0} HP Tối Đa của Resonator.
+          <t>Biến hình thành Rocksteady Guardian và bước vào Trạng Thái Né Đòn. Khi bị tấn công, gây Sát Thương Spectro bằng {0} HP Tối Đa của Resonator, và thực hiện đòn tấn công tiếp theo gây Sát Thương Spectro bằng {0} HP Tối Đa của Resonator.
 Sử dụng Kỹ Năng Echo một lần nữa để thoát khỏi trạng thái biến hình.
-Nếu đòn tấn công nhận được là đòn &lt;color=Highlight&gt;Special Skill&lt;/color&gt;, sẽ làm gián đoạn &lt;color=Highlight&gt;Special Skill&lt;/color&gt; của kẻ địch, nhận Shield tương đương 30% HP Tối Đa, và thực hiện đòn tấn công tiếp theo hai giai đoạn, mỗi giai đoạn gây Spectro DMG bằng {1} HP Tối Đa của Resonator. Những đòn tấn công tiếp theo này đồng thời phóng ra ba đợt sóng phá đất, mỗi đợt gây Spectro DMG bằng {2} HP Tối Đa của Resonator.
+Nếu đòn tấn công nhận được là đòn &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt;, sẽ làm gián đoạn &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; của kẻ địch, nhận Khiên tương đương 30% HP Tối Đa, và thực hiện đòn tấn công tiếp theo hai giai đoạn, mỗi giai đoạn gây Sát Thương Spectro bằng {1} HP Tối Đa của Resonator. Những đòn tấn công tiếp theo này đồng thời phóng ra ba đợt sóng phá đất, mỗi đợt gây Sát Thương Spectro bằng {2} HP Tối Đa của Resonator.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Khi ở trên chiến trường, Tấn Công tăng 5% mỗi 1.5 giây. Hiệu ứng này có thể chồng chất lên đến 4 lần. Sát Thương Outro Skill +60%.</t>
+          <t>Khi ở trên chiến trường, ATK tăng 5% mỗi 1.5 giây. Hiệu ứng này có thể chồng chất lên đến 4 lần. Sát Thương Kỹ Năng Outro +60%.</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Tấn Công và sát thương Outro Skill của người trang bị sẽ tăng khi ở trên chiến trường.</t>
+          <t>Khi ở trên chiến trường, ATK tăng 5% mỗi 1.5 giây. Hiệu ứng này có thể chồng chất lên đến 4 lần. Sát Thương Kỹ Năng Outro +60%.</t>
         </is>
       </c>
     </row>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công cho tất cả thành viên trong đội lên 15% trong 30 giây sau khi hồi máu cho đồng minh.</t>
+          <t>Tăng ATK cho tất cả thành viên trong đội lên 15% trong 30 giây sau khi hồi máu cho đồng minh.</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Increase Tấn Công cho tất cả thành viên trong đội khi hồi máu cho đồng minh.</t>
+          <t>Tăng ATK cho tất cả thành viên trong đội lên 15% trong 30 giây sau khi hồi máu cho đồng minh.</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Khi dùng Kỹ Năng Kết Thúc, tăng Tấn Công cho Resonator tiếp theo thêm 22.5% trong 15 giây.</t>
+          <t>Khi dùng Outro Skill, tăng ATK cho Resonator tiếp theo thêm 22.5% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Khi dùng Kỹ Năng Kết Thúc, tăng Tấn Công cho Resonator tiếp theo</t>
+          <t>Khi dùng Outro Skill, tăng ATK cho Resonator tiếp theo thêm 22.5% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>DMG Xoay Cộng Hưởng</t>
+          <t>Sát Thương Xoay Hòa Nhịp</t>
         </is>
       </c>
     </row>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>DMG Xoáy Cộng Hưởng</t>
+          <t>Sát Thương Xoáy Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>DMG Tiếng Vang Cộng Hưởng Giai Đoạn 1</t>
+          <t>Sát Thương Giai Đoạn 1 Vọng Âm</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>DMG Tiếng Vang Cộng Hưởng Giai Đoạn 2</t>
+          <t>Sát Thương Giai Đoạn 2 Vọng Âm</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Xoay Cộng Hưởng Concerto Regen</t>
+          <t>Hồi Phục Bản Hòa Tấu Xoay Hòa Nhịp</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Tiếng Vang Cộng Hưởng Concerto Regen</t>
+          <t>Hồi Phục Bản Hòa Tấu Vọng Âm</t>
         </is>
       </c>
     </row>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Summon Nhạc Công Trống chơi Bản Hủy Diệt. Đồng đội nhặt được Bản Hủy Diệt sẽ nhận hiệu ứng sau trong 10 giây: Khi Resonator tấn công mục tiêu, Nhạc Công Trống sẽ gây {0} Sát Thương Hỗn Loạn lên mục tiêu đó, tối đa 10 lần.
+          <t>Triệu hồi Nhạc Công Trống chơi Bản Hủy Diệt. Đồng đội nhặt được Bản Hủy Diệt sẽ nhận hiệu ứng sau trong 10 giây: Khi Resonator tấn công mục tiêu, Nhạc Công Trống sẽ gây {0} Sát Thương Hỗn Loạn lên mục tiêu đó, tối đa 10 lần.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -17374,9 +17374,9 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Tấn công kẻ địch phía trước, gây {0} Electro DMG, đồng thời triệu hồi Rác Cơ Khí tấn công. Rác Cơ Khí gây {1} Electro DMG khi trúng đích và phát nổ sau một lúc, gây {2} Electro DMG.
-Sau khi sử dụng Kỹ Năng Vọng Âm này, Tấn Công của nhân vật hiện tại tăng {3} trong {4} giây.
-Sát thương do Rác Cơ Khí gây ra bằng với Sát Thương Outro Skill của Resonator.
+          <t>ATK kẻ địch phía trước, gây {0} Sát Thương Electro, đồng thời triệu hồi Rác Cơ Khí tấn công. Rác Cơ Khí gây {1} Sát Thương Electro khi trúng đích và phát nổ sau một lúc, gây {2} Sát Thương Electro.
+Sau khi sử dụng Kỹ Năng Vọng Âm này, ATK của nhân vật hiện tại tăng {3} trong {4} giây.
+DMG do Rác Cơ Khí gây ra bằng với Sát Thương Kỹ Năng Outro của Resonator.
 Hồi chiêu: {5} giây</t>
         </is>
       </c>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Summon Nhạc Công Trống hỗ trợ đồng đội bằng các đòn tấn công gây Sát Thương Hỗn Loạn.</t>
+          <t>Triệu hồi Nhạc Công Trống hỗ trợ đồng đội bằng các đòn tấn công gây Sát Thương Hỗn Loạn.</t>
         </is>
       </c>
     </row>
@@ -17509,8 +17509,8 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo để triệu hồi một phần sức mạnh của *Sai Lầm Vô Hồi*, gây vụ nổ trong phạm vi xung quanh, gây Spectro DMG bằng {0} HP tối đa. Sau đó, Resonator nhận 10% hồi năng lượng cộng thêm và toàn bộ thành viên đội nhận 10% Tấn Công cộng thêm trong 20 giây.
-Giữ Kỹ Năng Echo để tung ra hàng loạt đòn tấn công liên tiếp tiêu hao STA, mỗi đòn gây Spectro DMG bằng {1} HP tối đa; thả ra để kết thúc bằng một đòn mạnh, gây Spectro DMG bằng {2} HP tối đa.
+          <t>Kích hoạt Kỹ Năng Tiếng Vọng để triệu hồi một phần sức mạnh của *Sai Lầm Vô Hồi*, gây vụ nổ trong phạm vi xung quanh, gây Sát Thương Spectro bằng {0} HP tối đa. Sau đó, Resonator nhận 10% hồi năng lượng cộng thêm và toàn bộ thành viên đội nhận 10% ATK cộng thêm trong 20 giây.
+Giữ Kỹ Năng Tiếng Vọng để tung ra hàng loạt đòn tấn công liên tiếp tiêu hao STA, mỗi đòn gây Sát Thương Spectro bằng {1} HP tối đa; thả ra để kết thúc bằng một đòn mạnh, gây Sát Thương Spectro bằng {2} HP tối đa.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -17579,9 +17579,9 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Kỹ Năng Echo để biến hình thành Voidwing Moth, gây {0} Spectro DMG lên kẻ địch xung quanh.
-Giữ Kỹ Năng Echo để tấn công liên tục, gây tối đa 12 lần {1} Spectro DMG.
-Trong vòng {2} giây sau khi dùng Kỹ Năng Echo này, sử dụng Outro Skill sẽ tăng Tấn Công của Resonator kế tiếp thêm {3} trong {4} giây.
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Echo để biến hình thành Voidwing Moth, gây {0} Sát Thương Spectro lên kẻ địch xung quanh.
+Giữ Kỹ Năng Echo để tấn công liên tục, gây tối đa 12 lần {1} Sát Thương Spectro.
+Trong vòng {2} giây sau khi dùng Kỹ Năng Echo này, sử dụng Kỹ Năng Outro sẽ tăng ATK của Resonator kế tiếp thêm {3} trong {4} giây.
 Hồi chiêu: {5} giây</t>
         </is>
       </c>
@@ -17649,9 +17649,9 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Kỹ Năng Echo để biến hình thành Voidwing Moth, gây Spectro DMG.
-Giữ Kỹ Năng Echo để tấn công liên tục, gây Spectro DMG.
-Sử dụng Kỹ Năng Echo này sẽ tăng Tấn Công của Resonator kế tiếp.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Echo để biến hình thành Voidwing Moth, gây Sát Thương Spectro.
+Giữ Kỹ Năng Echo để tấn công liên tục, gây Sát Thương Spectro.
+Sử dụng Kỹ Năng Echo này sẽ tăng ATK của Resonator kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -17716,7 +17716,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Summon một phần sức mạnh của Fallacy of Không Return để tung ra những đòn đánh uy lực, tăng hồi năng lượng cho Resonator và tăng Tấn Công cho tất cả thành viên trong đội.</t>
+          <t>Triệu hồi một phần sức mạnh của Fallacy of No Return để tung ra những đòn đánh uy lực, tăng hồi năng lượng cho Resonator và tăng ATK cho tất cả thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
       <c r="M360" t="inlineStr">
         <is>
           <t>Calcharo thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Skill này sẽ bước vào Cooldown chiêu nếu Calcharo rời khỏi chiến trường hoặc Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; không được kích hoạt trong một khoảng thời gian.
+Skill này sẽ bước vào Thời gian hồi chiêu nếu Calcharo rời khỏi chiến trường hoặc Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; không được kích hoạt trong một khoảng thời gian.
 Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; không làm gián đoạn chu kỳ Basic Attack của Calcharo.</t>
         </is>
       </c>
@@ -32253,7 +32253,7 @@
           <t>Các &lt;color=Highlight&gt;Normal Attacks&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; tiêu hao Nụ Crimson để nhận thêm Concerto Energy và &lt;color=Highlight&gt;Crimson Buds&lt;/color&gt;.
 Khi Concerto Energy đầy, kích hoạt &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; của Forte Circuit, hồi phục Nụ Crimson đồng thời tăng cường sức tấn công của Camellya.
 &lt;size=40&gt;&lt;color=Title&gt;Forte Circuit: Ephemeral&lt;/color&gt;&lt;/size&gt;
-Khi Concerto Energy đầy, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; miễn là &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; không trong Cooldown chiêu.
+Khi Concerto Energy đầy, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; miễn là &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; không trong Thời gian hồi chiêu.
 Tiêu hao Concerto Energy để gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và bước vào &lt;color=Highlight&gt;Budding Mode&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Budding Mode&lt;/color&gt;&lt;/size&gt;
@@ -32620,7 +32620,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Thời Gian Lung Linh</t>
+          <t>Thời Gian Lấp Lánh</t>
         </is>
       </c>
     </row>
@@ -32685,7 +32685,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Basic Attack</t>
+          <t>DMG Giai đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Basic Attack</t>
+          <t>DMG Giai đoạn 2 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Basic Attack</t>
+          <t>DMG Giai đoạn 3 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -32880,7 +32880,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 4 của Basic Attack</t>
+          <t>Sát Thương Cú Đòn Cơ Bản Hạng 4</t>
         </is>
       </c>
     </row>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -33010,7 +33010,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -33075,7 +33075,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Stage 2 Đòn Mid-air Attack – Lưỡi Hái: Sát Thương Phân Thể</t>
+          <t>Giai Đoạn 2 Đòn Mid-air Attack – Lưỡi Hái: Dissection DMG</t>
         </is>
       </c>
     </row>
@@ -33140,7 +33140,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Stage 3 Đòn Mid-air Attack – Lưỡi Hái: Sát Thương Phân Thể</t>
+          <t>Giai Đoạn 3 Đòn Mid-air Attack – Lưỡi Hái: Dissection DMG</t>
         </is>
       </c>
     </row>
@@ -33205,7 +33205,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Stage 2 Đòn Mid-air Attack – Lưỡi Hái: Sát Thương Cộng Hưởng</t>
+          <t>Giai Đoạn 2 Đòn Mid-air Attack – Lưỡi Hái: Resction DMG</t>
         </is>
       </c>
     </row>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Stage 3 Đòn Mid-air Attack – Lưỡi Hái: Sát Thương Cộng Hưởng</t>
+          <t>Giai Đoạn 3 Đòn Mid-air Attack – Lưỡi Hái: Resction DMG</t>
         </is>
       </c>
     </row>
@@ -33335,7 +33335,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Stage 4 Đòn Mid-air Attack: Sát Thương</t>
+          <t>Giai Đoạn 4 Đòn Mid-air Attack: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -33400,7 +33400,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Sát thương Phản đòn Dodge Ground</t>
+          <t>DMG Phản đòn Né tránh Mặt đất</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>DMG từ Mid-air Dodge Counter</t>
+          <t>Sát Thương Dodge Counter Tránh Trên Không</t>
         </is>
       </c>
     </row>
@@ -33530,7 +33530,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>DMG Dòng Chảy Vàng</t>
+          <t>Sát Thương Dòng Chảy Vàng</t>
         </is>
       </c>
     </row>
@@ -33595,7 +33595,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Vòng Thi Hành: DMG Vòng Tròn</t>
+          <t>Aureole of Execution: Ring DMG</t>
         </is>
       </c>
     </row>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Vòng Thi Hành: DMG Phá Vỡ</t>
+          <t>Aureole of Execution: Breach DMG</t>
         </is>
       </c>
     </row>
@@ -33725,7 +33725,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Vòng Thi Hành: DMG Chói Lòa</t>
+          <t>Aureole of Execution: Glare DMG</t>
         </is>
       </c>
     </row>
@@ -33855,7 +33855,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>DMG Búa Địa Chấn</t>
+          <t>Sát Thương Khúc Giao Hưởng Đại Địa Chấn</t>
         </is>
       </c>
     </row>
@@ -33920,7 +33920,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Sát Thương Ichor Deposit</t>
+          <t>Sát Thương Kho Dưỡng Chất</t>
         </is>
       </c>
     </row>
@@ -34050,7 +34050,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Dòng Chảy Vàng</t>
+          <t>Thời gian hồi Chiêu Dòng Chảy Vàng</t>
         </is>
       </c>
     </row>
@@ -34115,7 +34115,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Vòng Thi Hành Concerto Regen</t>
+          <t>Khúc Tái Sinh của Aureole Hành Quyết</t>
         </is>
       </c>
     </row>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Búa Địa Chấn Concerto Regen</t>
+          <t>Hồi Phục Khúc Giao Hưởng Đại Địa Chấn</t>
         </is>
       </c>
     </row>
@@ -34245,7 +34245,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Tiêu hao Resonance Energy</t>
+          <t>Chi Phí Resonance Energy</t>
         </is>
       </c>
     </row>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -34635,7 +34635,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Sát Thương Ichor Blade (mỗi 0.15 giây)</t>
+          <t>Sát Thương Kiếm Dịch Huyết (mỗi 0.15 giây)</t>
         </is>
       </c>
     </row>
@@ -34700,7 +34700,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Tăng Hệ Số Nhân DMG Thẩm Phán Vàng</t>
+          <t>Tăng hệ số DMG của Aureate Judge</t>
         </is>
       </c>
     </row>
